--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-06).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-06).xlsx
@@ -47,7 +47,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -57,11 +57,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8EEF5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,9 +101,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -909,21 +901,25 @@
         <v>919490481</v>
       </c>
       <c r="F9" s="4" t="n"/>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Yakkabog' tumani</t>
+        </is>
+      </c>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>4-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Yakkabog' tumani 4-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>General Secondary School No. 4</t>
+          <t>General Secondary School No. 4, Yakkabog District</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Общеобразовательная школа №4</t>
+          <t>Общеобразовательная школа №4 Яккабагского района</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -2243,21 +2239,25 @@
       <c r="F31" s="4" t="n">
         <v>770867725</v>
       </c>
-      <c r="G31" s="7" t="n"/>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Yakkabog' tumani</t>
+        </is>
+      </c>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Yakkabog' tumani 45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>General Secondary School No. 45</t>
+          <t>General Secondary School No. 45, Yakkabog District</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>Общеобразовательная школа №45</t>
+          <t>Общеобразовательная школа №45 Яккабагского района</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-06).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-06).xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,37 +27,15 @@
     </font>
     <font>
       <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="001E3A8A"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <i val="1"/>
-      <color rgb="00555555"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF5"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -86,22 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,2176 +435,2039 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A3:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4.5" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="17.5" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="16.5" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="3.14" customWidth="1" min="1" max="1"/>
+    <col width="34.43" customWidth="1" min="2" max="2"/>
+    <col width="17.29" customWidth="1" min="3" max="3"/>
+    <col width="13.43" customWidth="1" min="4" max="4"/>
+    <col width="17.86" customWidth="1" min="5" max="5"/>
+    <col width="22.57" customWidth="1" min="6" max="6"/>
+    <col width="21.71" customWidth="1" min="7" max="7"/>
+    <col width="17.71" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="26.29" customWidth="1" min="10" max="10"/>
+    <col width="13.86" customWidth="1" min="11" max="11"/>
+    <col width="16.43" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Guruh 26-06 (34 nafar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Namuna: Saydalimov Anvarjon Sarvarjon o`g`li | 517******0016 | AC1686958 | 990201527 | Qashqadaryo, Qarshi | 4-mittituman 21/23 | Qarshi shahar 1-maktab | Qarshi City School No. 1 | Школа №1 города Карши | Maktab | AA1775603 | 2008-2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="63" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="47.25" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>F.I.O</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>JSHSHIR</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Pasport seriya raqami</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>2-Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Yashash viloyat+tumani</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>UY manzili</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Uzbek tilida)</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Ingliz tilida)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Avval o`qigan muassasa nomi(Rus tilida)</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Maktab, kollej va HK</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Avval olgan diplom seriya+raqami</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Boshlagan va tugatgan yili</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="n">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Abdinazarova Dilafro'z Burxon qizi</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>40401955680037</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>AE3704528</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="2" t="n">
         <v>903410676</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="2" t="n">
         <v>918980495</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Kitob iqtisodiyot kolleji</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Kitob College of Economics</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>Китабский экономический колледж</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>K 3745934</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>2012-2015</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Abdixoliqova Elmira Farxod qizi</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>62501095720012</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>AE4512271</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="2" t="n">
         <v>971100325</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="2" t="n">
         <v>910710683</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 36, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №36 города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>UM 03718322</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Azimova Zahroxon Abdirauf qizi</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>61312065590013</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>AD5290004</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="2" t="n">
         <v>977997671</v>
       </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 2-son kasb-hunar maktabi</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Vocational School No. 2, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>Профессиональная школа №2 города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>PT 0176926</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>2021-2024</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Bahodirova Asila Olmos qizi</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>61711085590032</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>AE1222596</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="2" t="n">
         <v>776021708</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="2" t="n">
         <v>702191108</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 7, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №7 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>UM 03753386</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Davlatova Gulnoza Husan qizi</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>41508955590021</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>AD8208717</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="2" t="n">
         <v>887886042</v>
       </c>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Yengil sanoat kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Vocational College of Light Industry</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>Шахрисабзский профессиональный колледж лёгкой промышленности</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>K 0216332</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>2011-2014</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Eshimova Zilola Bekzod qizi</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>61506085730076</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>AE2935693</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="2" t="n">
         <v>919490481</v>
       </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 4-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 4, Yakkabog District</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №4 Яккабагского района</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>UM 03756027</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Irgasheva Dinora Shodmon qizi</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>60106035590029</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>AC2430931</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani 14-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>General Secondary School No. 14, Shahrisabz District</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Maktab</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>UM 0441030</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2015-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>60603085590037</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>AD9937321</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E11" s="2" t="n">
         <v>919524344</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F11" s="2" t="n">
         <v>904422247</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 23, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №23 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>UM 03752997</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>60907085590063</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>AE6299685</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E12" s="2" t="n">
         <v>950202813</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F12" s="2" t="n">
         <v>950702813</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 23, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №23 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>UM 03752998</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>61502085680047</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>AE4674508</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E13" s="2" t="n">
         <v>700349505</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F13" s="2" t="n">
         <v>994688406</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 46, Kitob District</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №46 Китабского района</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>UM 03729342</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Mahmadmurodova Sevara Safarali qizi</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>60705005680087</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>AE2103843</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E14" s="2" t="n">
         <v>996739929</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F14" s="2" t="n">
         <v>973194003</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Kitob agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Kitob Vocational College of Agribusiness</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>Китабский профессиональный колледж агробизнеса</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>K 5493345</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Mahmatqulova Nilufar Qayum qizi</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>60806085590115</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>AE6047826</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E15" s="2" t="n">
         <v>883848545</v>
       </c>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 43-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 43, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №43 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>UM 03754788</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>2013-2024</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>61707085680068</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>AE4270256</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E16" s="2" t="n">
         <v>332960708</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F16" s="2" t="n">
         <v>881360926</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 81-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 81, Kitob District</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №81 Китабского района</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>UM 03730531</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>60710085680047</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>AE4263249</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E17" s="2" t="n">
         <v>887326111</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F17" s="2" t="n">
         <v>906176883</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 32, Kitob District</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №32 Китабского района</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>UM 03728995</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Maxmarajabova Zerda Hasan qizi</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>60106075720246</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>AE5221552</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E18" s="2" t="n">
         <v>912171430</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F18" s="2" t="n">
         <v>941343403</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 35-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 35, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №35 города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>UM 03718284</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>63001085590111</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>AE2259069</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E19" s="2" t="n">
         <v>883887912</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F19" s="2" t="n">
         <v>877160130</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 20, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №20 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>UM 03752895</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Mustafayeva Nargiza Ulug'bek qizi</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>62906005590060</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>AB8521319</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E20" s="2" t="n">
         <v>883990096</v>
       </c>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Vocational College of Pedagogy and Tourism</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>Шахрисабзский профессиональный колледж педагогики и туризма</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>K 5487472</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>60506085590066</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>AE2428256</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E21" s="2" t="n">
         <v>876590027</v>
       </c>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 7, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №7 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>UM 03751925</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Narziyeva Intizor Iskandar qizi</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>40211995680023</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>AB5359926</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Kitob sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Kitob Vocational College of Industry and Services</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>Китабский профессиональный колледж промышленности и сервиса</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>K 5047841</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>2015-2018</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Niyozova Sevara Turoqulovna</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>41206892560120</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>AD9706738</t>
         </is>
       </c>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz qishloq xo'jaligi kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Agricultural Vocational College</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>Шахрисабзский сельскохозяйственный профессиональный колледж</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>K 0998119</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>2005-2008</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>60504085680019</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>AD9494409</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E24" s="2" t="n">
         <v>770683017</v>
       </c>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 46, Kitob District</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №46 Китабского района</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>UM 03729348</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>62012045590040</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>AD0776916</t>
         </is>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E25" s="2" t="n">
         <v>888298280</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F25" s="2" t="n">
         <v>883038280</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 8, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №8 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>UM 1313018</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>2011-2022</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>62201085590064</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>AE2118072</t>
         </is>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E26" s="2" t="n">
         <v>933565022</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F26" s="2" t="n">
         <v>910901627</v>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 23, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №23 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>UM 03753960</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>62911085630012</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>AE1143288</t>
         </is>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E27" s="2" t="n">
         <v>976188504</v>
       </c>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Chiroqchi tumani</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Chiroqchi tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Chiroqchi District</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №70 Чиракчинского района</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>UM 03742130</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>62702085680028</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>AE4246251</t>
         </is>
       </c>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 36, Kitob District</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №36 Китабского района</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>UM 03729118</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>62201085590019</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>AD8686485</t>
         </is>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E29" s="2" t="n">
         <v>885581535</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F29" s="2" t="n">
         <v>886331535</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 5, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №5 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>UM 03751785</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>60409015590065</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>AC1805235</t>
         </is>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E30" s="2" t="n">
         <v>888191006</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F30" s="2" t="n">
         <v>888606150</v>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Miroq sport pedagogika kolleji</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Miroq Sports and Pedagogical College</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>Мирокский спортивно-педагогический колледж</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>K 5509185</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Sayfieva Sarvinoz Zafar qizi</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>41507985590074</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>AB6304158</t>
         </is>
       </c>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz qurilish va maishiy texnikalar kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Vocational College of Construction and Household Appliances</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>Шахрисабзский профессиональный колледж строительства и бытовой техники</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>K 4587984</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>2015-2018</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>62203085730015</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>AE4385111</t>
         </is>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E32" s="2" t="n">
         <v>931522577</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F32" s="2" t="n">
         <v>770867725</v>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 45, Yakkabog District</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №45 Яккабагского района</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>UM 03757340</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>62408065590018</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>AD2624840</t>
         </is>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E33" s="2" t="n">
         <v>770209066</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F33" s="2" t="n">
         <v>991638468</v>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №15 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>UM 01922678</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>2012-2023</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>42601925680010</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>AB5702170</t>
         </is>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E34" s="2" t="n">
         <v>970662692</v>
       </c>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Mahrid Vocational College of Agribusiness</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>Махридский профессиональный колледж агробизнеса</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>K 1994177</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>2008-2011</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>40712902560079</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>AE4385291</t>
         </is>
       </c>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Qamashi tumani</t>
         </is>
       </c>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Qamashi tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 8, Qamashi District</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №8 Камашинского района</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>O'R-A 5263487</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>1997-2008</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>61604065590015</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>AD2922676</t>
         </is>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E36" s="2" t="n">
         <v>908631674</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F36" s="2" t="n">
         <v>908810610</v>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №15 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>UM 02172469</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>2013-2024</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>62802085680012</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>AE4629898</t>
         </is>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E37" s="2" t="n">
         <v>773710028</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F37" s="2" t="n">
         <v>956652882</v>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 46, Kitob District</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №46 Китабского района</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>UM 03729356</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>63007085680074</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>AE4688777</t>
         </is>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E38" s="2" t="n">
         <v>905181884</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F38" s="2" t="n">
         <v>875613002</v>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 32, Kitob District</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №32 Китабского района</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>UM 03729007</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-06).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-06).xlsx
@@ -435,22 +435,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:M38"/>
+  <dimension ref="A3:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.14" customWidth="1" min="1" max="1"/>
-    <col width="34.43" customWidth="1" min="2" max="2"/>
-    <col width="17.29" customWidth="1" min="3" max="3"/>
-    <col width="13.43" customWidth="1" min="4" max="4"/>
-    <col width="17.86" customWidth="1" min="5" max="5"/>
-    <col width="22.57" customWidth="1" min="6" max="6"/>
-    <col width="21.71" customWidth="1" min="7" max="7"/>
-    <col width="17.71" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="26.29" customWidth="1" min="10" max="10"/>
-    <col width="13.86" customWidth="1" min="11" max="11"/>
-    <col width="16.43" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34.43" customWidth="1" min="3" max="3"/>
+    <col width="17.29" customWidth="1" min="4" max="4"/>
+    <col width="13.43" customWidth="1" min="5" max="5"/>
+    <col width="17.86" customWidth="1" min="6" max="6"/>
+    <col width="22.57" customWidth="1" min="7" max="7"/>
+    <col width="21.71" customWidth="1" min="8" max="8"/>
+    <col width="17.71" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="26.29" customWidth="1" min="11" max="11"/>
+    <col width="13.86" customWidth="1" min="12" max="12"/>
+    <col width="16.43" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="3" ht="47.25" customHeight="1">
@@ -461,60 +462,65 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
+          <t>Guruhi</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
           <t>F.I.O</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>JSHSHIR</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Pasport seriya raqami</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>2-Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Yashash viloyat+tumani</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>UY manzili</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Uzbek tilida)</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Ingliz tilida)</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Maktab, kollej va HK</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Avval olgan diplom seriya+raqami</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>Boshlagan va tugatgan yili</t>
         </is>
@@ -526,52 +532,57 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>Abdinazarova Dilafro'z Burxon qizi</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>40401955680037</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>AE3704528</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>903410676</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>918980495</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Kitob iqtisodiyot kolleji</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Kitob College of Economics</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>K 3745934</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2012-2015</t>
         </is>
@@ -583,52 +594,57 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>Abdixoliqova Elmira Farxod qizi</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>62501095720012</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>AE4512271</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>971100325</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>910710683</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 36, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>UM 03718322</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -640,50 +656,55 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>Azimova Zahroxon Abdirauf qizi</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>61312065590013</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>AD5290004</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>977997671</v>
       </c>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 2-son kasb-hunar maktabi</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Vocational School No. 2, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>PT 0176926</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2021-2024</t>
         </is>
@@ -695,52 +716,57 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>Bahodirova Asila Olmos qizi</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>61711085590032</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>AE1222596</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>776021708</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>702191108</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 7, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>UM 03753386</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -752,50 +778,55 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>Davlatova Gulnoza Husan qizi</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>41508955590021</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>AD8208717</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>887886042</v>
       </c>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Yengil sanoat kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Vocational College of Light Industry</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>K 0216332</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>2011-2014</t>
         </is>
@@ -807,50 +838,55 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>Eshimova Zilola Bekzod qizi</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>61506085730076</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>AE2935693</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>919490481</v>
       </c>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 4-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 4, Yakkabog District</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>UM 03756027</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -862,48 +898,53 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>Irgasheva Dinora Shodmon qizi</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>60106035590029</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>AC2430931</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 14-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 14, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>UM 0441030</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -915,52 +956,57 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>Jalilova Shabnam Ozodjon qizi</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>60603085590037</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>AD9937321</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>919524344</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>904422247</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 23, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>UM 03752997</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -972,52 +1018,57 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>Jumayeva Husnida Shovkat qizi</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>60907085590063</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>AE6299685</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>950202813</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="G12" s="2" t="n">
         <v>950702813</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 23, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>UM 03752998</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1029,52 +1080,57 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>61502085680047</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>AE4674508</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="F13" s="2" t="n">
         <v>700349505</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="G13" s="2" t="n">
         <v>994688406</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 46, Kitob District</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>UM 03729342</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1086,52 +1142,57 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>Mahmadmurodova Sevara Safarali qizi</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>60705005680087</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>AE2103843</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="F14" s="2" t="n">
         <v>996739929</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="G14" s="2" t="n">
         <v>973194003</v>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Kitob agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Kitob Vocational College of Agribusiness</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>K 5493345</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
@@ -1143,50 +1204,55 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>Mahmatqulova Nilufar Qayum qizi</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>60806085590115</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>AE6047826</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="F15" s="2" t="n">
         <v>883848545</v>
       </c>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 43-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 43, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>UM 03754788</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>2013-2024</t>
         </is>
@@ -1198,52 +1264,57 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>Mahmudova Maftuna To'ra qizi</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>61707085680068</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>AE4270256</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="F16" s="2" t="n">
         <v>332960708</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>881360926</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 81-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 81, Kitob District</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>UM 03730531</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1255,52 +1326,57 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>Mannonova Shahrizoda Nosir qizi</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>60710085680047</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>AE4263249</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="F17" s="2" t="n">
         <v>887326111</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>906176883</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 32, Kitob District</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>UM 03728995</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1312,52 +1388,57 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>Maxmarajabova Zerda Hasan qizi</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>60106075720246</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>AE5221552</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="F18" s="2" t="n">
         <v>912171430</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>941343403</v>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 35-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 35, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>UM 03718284</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1369,52 +1450,57 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
           <t>Muminova Sevinch Uchqun qizi</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>63001085590111</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>AE2259069</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="F19" s="2" t="n">
         <v>883887912</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="G19" s="2" t="n">
         <v>877160130</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 20, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>UM 03752895</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1426,50 +1512,55 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>Mustafayeva Nargiza Ulug'bek qizi</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>62906005590060</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>AB8521319</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="F20" s="2" t="n">
         <v>883990096</v>
       </c>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz pedagogika va turizm kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Vocational College of Pedagogy and Tourism</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>K 5487472</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
@@ -1481,50 +1572,55 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>Muxtorova Xadicha Zaxriddin qizi</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>60506085590066</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>AE2428256</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="F21" s="2" t="n">
         <v>876590027</v>
       </c>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 7-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 7, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>UM 03751925</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1536,48 +1632,53 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
           <t>Narziyeva Intizor Iskandar qizi</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>40211995680023</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>AB5359926</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Kitob sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Kitob Vocational College of Industry and Services</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>K 5047841</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2015-2018</t>
         </is>
@@ -1589,48 +1690,53 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>Niyozova Sevara Turoqulovna</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>41206892560120</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>AD9706738</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz qishloq xo'jaligi kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Agricultural Vocational College</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>K 0998119</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>2005-2008</t>
         </is>
@@ -1642,50 +1748,55 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
           <t>Nurillayeva Sevinch Mashrab qizi</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>60504085680019</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>AD9494409</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="F24" s="2" t="n">
         <v>770683017</v>
       </c>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 46, Kitob District</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>UM 03729348</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1697,52 +1808,57 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
           <t>Ortiqova Dilnoza Zokir qizi</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>62012045590040</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>AD0776916</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="F25" s="2" t="n">
         <v>888298280</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>883038280</v>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 8, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>UM 1313018</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2011-2022</t>
         </is>
@@ -1754,52 +1870,57 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
           <t>Qarshiyeva Shahlo Talantjon qizi</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>62201085590064</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>AE2118072</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="F26" s="2" t="n">
         <v>933565022</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>910901627</v>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 23-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 23, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>UM 03753960</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1811,50 +1932,55 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
           <t>Quchqarova Zebiniso Farhod qizi</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>62911085630012</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>AE1143288</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="F27" s="2" t="n">
         <v>976188504</v>
       </c>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Chiroqchi tumani</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Chiroqchi tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Chiroqchi District</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>UM 03742130</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1866,48 +1992,53 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
           <t>Samiyeva Sevinchbonu Uyg'un qizi</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>62702085680028</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>AE4246251</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 36, Kitob District</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>UM 03729118</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1919,52 +2050,57 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
           <t>Sanaqulova Muxtarama Xudoyqulovna</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>62201085590019</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>AD8686485</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="F29" s="2" t="n">
         <v>885581535</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>886331535</v>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 5-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 5, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>UM 03751785</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1976,52 +2112,57 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
           <t>Sanaqulova Nozliya G'ofur qizi</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>60409015590065</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>AC1805235</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="F30" s="2" t="n">
         <v>888191006</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>888606150</v>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Miroq sport pedagogika kolleji</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Miroq Sports and Pedagogical College</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>K 5509185</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
@@ -2033,48 +2174,53 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
           <t>Sayfieva Sarvinoz Zafar qizi</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>41507985590074</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>AB6304158</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz qurilish va maishiy texnikalar kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Vocational College of Construction and Household Appliances</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>K 4587984</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>2015-2018</t>
         </is>
@@ -2086,52 +2232,57 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
           <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>62203085730015</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>AE4385111</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="F32" s="2" t="n">
         <v>931522577</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>770867725</v>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 45, Yakkabog District</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>UM 03757340</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -2143,52 +2294,57 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
           <t>Turayeva Gulasal Jura qizi</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>62408065590018</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>AD2624840</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="F33" s="2" t="n">
         <v>770209066</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>991638468</v>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>UM 01922678</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>2012-2023</t>
         </is>
@@ -2200,50 +2356,55 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
           <t>Usmonova Gulnoza Xamdam qizi</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>42601925680010</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>AB5702170</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="F34" s="2" t="n">
         <v>970662692</v>
       </c>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Mahrid Agrobiznes kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Mahrid Vocational College of Agribusiness</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>K 1994177</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>2008-2011</t>
         </is>
@@ -2255,48 +2416,53 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
           <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>40712902560079</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>AE4385291</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Qamashi tumani</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Qamashi tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 8, Qamashi District</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>O'R-A 5263487</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>1997-2008</t>
         </is>
@@ -2308,52 +2474,57 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
           <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>61604065590015</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>AD2922676</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="F36" s="2" t="n">
         <v>908631674</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>908810610</v>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>UM 02172469</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>2013-2024</t>
         </is>
@@ -2365,52 +2536,57 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
           <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>62802085680012</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>AE4629898</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="F37" s="2" t="n">
         <v>773710028</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>956652882</v>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 46, Kitob District</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>UM 03729356</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -2422,52 +2598,57 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
+          <t>26-06</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
           <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>63007085680074</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>AE4688777</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="F38" s="2" t="n">
         <v>905181884</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>875613002</v>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 32, Kitob District</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>UM 03729007</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-06).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-06).xlsx
@@ -551,17 +551,21 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>903410676</v>
+        <v>189804950</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>918980495</v>
+        <v>88308650</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Saray MFY, Yangiqishloq, 81-uy</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Kitob iqtisodiyot kolleji</t>
@@ -613,17 +617,21 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>971100325</v>
+        <v>887100325</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>910710683</v>
+        <v>884710683</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n"/>
+          <t>Qashqadaryo, Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Qirğiz MFY, Yoshlik kõchasi, 29-uy</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 36-sonli umumiy o'rta ta'lim maktabi</t>
@@ -677,13 +685,19 @@
       <c r="F6" s="2" t="n">
         <v>977997671</v>
       </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="2" t="n">
+        <v>884037671</v>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Kesh, Kalokon, 73 uy</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 2-son kasb-hunar maktabi</t>
@@ -742,10 +756,14 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Hojimaydon MFY, Chambil koʻchasi, 14-uy</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 7-sonli umumiy o'rta ta'lim maktabi</t>
@@ -797,15 +815,21 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>887886042</v>
-      </c>
-      <c r="G8" s="2" t="n"/>
+        <v>878860420</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>916383271</v>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Fayzobod MFY, Quruvchilar kuchasi, 68 uy</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Yengil sanoat kasb-hunar kolleji</t>
@@ -857,15 +881,21 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>919490481</v>
-      </c>
-      <c r="G9" s="2" t="n"/>
+        <v>198815080</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>904810912</v>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Darxon MFY, Eshonguzar, 52-uy</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 4-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1037,17 +1067,21 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>950202813</v>
+        <v>502028130</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>950702813</v>
+        <v>727528130</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>SinaboĝMFY, Sinaboĝ kuchasi, 133-uy</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 23-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1161,17 +1195,21 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>996739929</v>
+        <v>967399290</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>973194003</v>
+        <v>967399290</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Katlos MFY, Oshqon kuchasi, 69-uy</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Kitob agrobiznes kasb-hunar kolleji</t>
@@ -1283,7 +1321,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>332960708</v>
+        <v>329607080</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>881360926</v>
@@ -1293,7 +1331,11 @@
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Sariosiyo MFY, Chinorlik ko'chasi, 14.0</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 81-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1345,17 +1387,21 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>887326111</v>
+        <v>873261110</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>906176883</v>
+        <v>768830906</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Ulugʻbek MFY, Qizil darvoza kuchasi, 116.0</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 32-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1469,17 +1515,21 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>883887912</v>
+        <v>771601300</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>877160130</v>
+        <v>838879120</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Uymovut MFY, Ohangrabo ko'chasi, 97-uy</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 20-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1591,15 +1641,21 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>876590027</v>
-      </c>
-      <c r="G21" s="2" t="n"/>
+        <v>765900270</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>707908680</v>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Bunyodkor MFY, Paxtakor koʻchasi, 44/a</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 7-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1708,14 +1764,22 @@
           <t>AD9706738</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
+      <c r="F23" s="2" t="n">
+        <v>738656120</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>738246060</v>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Xujahurason mahallasi, Sugʻdiyona, 50 uy</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz qishloq xo'jaligi kasb-hunar kolleji</t>
@@ -1767,15 +1831,21 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>770683017</v>
-      </c>
-      <c r="G24" s="2" t="n"/>
+        <v>515384080</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>912849800</v>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Oqsuv MFY, Nimgi qishloq, 38_uy</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1834,10 +1904,14 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Miraki mahallasi, Navoiy, 84 uy</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1889,17 +1963,21 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>933565022</v>
+        <v>335650220</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>910901627</v>
+        <v>109016270</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Yomchi, Abdulqosim Firdavsiy, 134-uy</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 23-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1951,15 +2029,21 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>976188504</v>
-      </c>
-      <c r="G27" s="2" t="n"/>
+        <v>546564080</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>885040954</v>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="n"/>
+          <t>Qashqadaryo, Qamashi tumani</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Yuksalish MFY, Olmazor, 124.0</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Chiroqchi tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2010,14 +2094,22 @@
           <t>AE4246251</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
+      <c r="F28" s="2" t="n">
+        <v>50305390</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>919510536</v>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Nurafshon MFY, Kun botar, 101-uy</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 36-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2069,17 +2161,21 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>885581535</v>
+        <v>855815350</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>886331535</v>
+        <v>863315350</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Yashil diyor mfy, Yashil diyor kuchasi, 118.0</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 5-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2131,17 +2227,21 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>888191006</v>
+        <v>886061500</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>888606150</v>
+        <v>761500919</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Meraki MFY, NAVOIY KÖCHASI, 48.0</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Miroq sport pedagogika kolleji</t>
@@ -2192,14 +2292,22 @@
           <t>AB6304158</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
+      <c r="F31" s="2" t="n">
+        <v>505895877</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>871947276</v>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Boston MFY, Kenagaz, 73- uy</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz qurilish va maishiy texnikalar kasb-hunar kolleji</t>
@@ -2251,7 +2359,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>931522577</v>
+        <v>315225770</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>770867725</v>
@@ -2261,7 +2369,11 @@
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Yashnabod MFY, Faravon kochasi, 223-uy</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 45-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2313,17 +2425,21 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>770209066</v>
+        <v>702090660</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>991638468</v>
+        <v>976175037</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Ipak yuli, Ipak yuli, 128-uy</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2434,14 +2550,22 @@
           <t>AE4385291</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
+      <c r="F35" s="2" t="n">
+        <v>938918590</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>976350269</v>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Qamashi tumani</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Shamaton MFY, Yangiobod1, 111 uy</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Qamashi tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2493,17 +2617,21 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
+        <v>908810610</v>
+      </c>
+      <c r="G36" s="2" t="n">
         <v>908631674</v>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>908810610</v>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Fayzabod MFY, Quruvchilar ko'chasi, 73-uy</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2555,17 +2683,21 @@
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>773710028</v>
+        <v>737100280</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>956652882</v>
+        <v>566528820</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Oqsuv MFY, Yoshlar kuchasi, 156-uy</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2617,17 +2749,21 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>905181884</v>
+        <v>756130020</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>875613002</v>
+        <v>51818840</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Ulugʻbek MFY, Urigzor koʻchasi, 23 -uy</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 32-sonli umumiy o'rta ta'lim maktabi</t>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-06).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-06).xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:N38"/>
+  <dimension ref="A3:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.14" customWidth="1" min="1" max="1"/>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>189804950</v>
+        <v>918980495</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>88308650</v>
+        <v>908830865</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -690,12 +690,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shaxar</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Kesh, Kalokon, 73 uy</t>
+          <t>Kesh mahalas, Kalakon kuchas, 73-uy</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>878860420</v>
+        <v>887886042</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>916383271</v>
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>198815080</v>
+        <v>919881508</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>904810912</v>
+        <v>912237520</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Yakkabog' tumani</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Darxon MFY, Eshonguzar, 52-uy</t>
+          <t>Darxon MFY, Eshonguzar kôchasi, 52-uy</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -946,14 +946,22 @@
           <t>AC2430931</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
+      <c r="F10" s="2" t="n">
+        <v>915626577</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>918127080</v>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz Shahar</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Farovon, Farovon kuchasi, 14-uy</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 14-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1005,17 +1013,21 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
+        <v>778108280</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>919524344</v>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>904422247</v>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shaxar</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Sinabog MFY, oqshom, 112-uy</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 23-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1067,14 +1079,14 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>502028130</v>
+        <v>950202813</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>727528130</v>
+        <v>772752813</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shaxrisabiz shahar</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1195,10 +1207,10 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>967399290</v>
+        <v>996739929</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>967399290</v>
+        <v>996739929</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1207,7 +1219,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Katlos MFY, Oshqon kuchasi, 69-uy</t>
+          <t>Katlos MFY, Oshqon, 69-uy</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1321,7 +1333,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>329607080</v>
+        <v>332960708</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>881360926</v>
@@ -1333,7 +1345,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Sariosiyo MFY, Chinorlik ko'chasi, 14.0</t>
+          <t>Sariosiyo MFY, Chinorlik koʻchasi, 14-uy</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1387,10 +1399,10 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>873261110</v>
+        <v>887326111</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>768830906</v>
+        <v>916176883</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1399,7 +1411,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Ulugʻbek MFY, Qizil darvoza kuchasi, 116.0</t>
+          <t>Ulugʻbek MFY, Qizil darvoza kuchasi, 116-uy</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1453,17 +1465,21 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>912171430</v>
+        <v>882446808</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>941343403</v>
+        <v>880271582</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n"/>
+          <t>Qashqadaryo, Chiroqchi</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Hamid olimjon MFY, Haytkul, 115-uy</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 35-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1515,14 +1531,14 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>771601300</v>
+        <v>877160130</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>838879120</v>
+        <v>883887912</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1641,14 +1657,14 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>765900270</v>
+        <v>876590027</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>707908680</v>
+        <v>870790868</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahrar</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1765,19 +1781,19 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>738656120</v>
+        <v>973865612</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>738246060</v>
+        <v>973824606</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Xujahurason mahallasi, Sugʻdiyona, 50 uy</t>
+          <t>Xujahurason mahalla, Sugʻdiyona, 50-uy</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1831,10 +1847,10 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>515384080</v>
+        <v>951538408</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>912849800</v>
+        <v>991284980</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1843,7 +1859,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Oqsuv MFY, Nimgi qishloq, 38_uy</t>
+          <t>Oqsuv, Nimgi qishloq, 38-uy</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1904,12 +1920,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Miraki</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Miraki mahallasi, Navoiy, 84 uy</t>
+          <t>Alisher Navoiy, Navoiy kuchasi, 84 uy</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1963,19 +1979,19 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>335650220</v>
+        <v>933565022</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>109016270</v>
+        <v>910901627</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Yomchi, Abdulqosim Firdavsiy, 134-uy</t>
+          <t>Q9oʻrgʻon tepa MFY, Abdulqodimfirdavsiy koʻchasi, 134-uy</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2029,10 +2045,10 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>546564080</v>
+        <v>954656408</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>885040954</v>
+        <v>976188504</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2041,7 +2057,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Yuksalish MFY, Olmazor, 124.0</t>
+          <t>Yuksalish MFY, Olmazor koʻchasi, 124-uy</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2095,7 +2111,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>50305390</v>
+        <v>505030539</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>919510536</v>
@@ -2161,10 +2177,10 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>855815350</v>
+        <v>885581535</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>863315350</v>
+        <v>886331535</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2173,7 +2189,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Yashil diyor mfy, Yashil diyor kuchasi, 118.0</t>
+          <t>Yashil diyor 116, Yashil diyor kuchasi, 118 uy</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2227,19 +2243,19 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>886061500</v>
+        <v>888606150</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>761500919</v>
+        <v>908776150</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shaxrisabz tumani</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Meraki MFY, NAVOIY KÖCHASI, 48.0</t>
+          <t>Meraki MFY, NAVOIY KÖCHASI, 48-uy</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2300,7 +2316,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2359,14 +2375,14 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>315225770</v>
+        <v>931522577</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>770867725</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Yakkabog' tumani</t>
+          <t>Qashqadaryo, Yakkaboğ tumani</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2425,14 +2441,14 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>702090660</v>
+        <v>770209066</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>976175037</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2537,43 +2553,43 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>40712902560079</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>AE4385291</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>938918590</v>
+        <v>908810610</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>976350269</v>
+        <v>908631674</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Shamaton MFY, Yangiobod1, 111 uy</t>
+          <t>Fayzabod MFY, Quruvchilar ko'chasi, 73-uy</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Qamashi tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>General Secondary School No. 8, Qamashi District</t>
+          <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2583,12 +2599,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>O'R-A 5263487</t>
+          <t>UM 02172469</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1997-2008</t>
+          <t>2013-2024</t>
         </is>
       </c>
     </row>
@@ -2603,43 +2619,43 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>908810610</v>
+        <v>773710028</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>908631674</v>
+        <v>956652882</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Fayzabod MFY, Quruvchilar ko'chasi, 73-uy</t>
+          <t>Oqsuv MFY, Nimgi qishlog'i, 156uy</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>General Secondary School No. 15, Shahrisabz District</t>
+          <t>General Secondary School No. 46, Kitob District</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -2649,12 +2665,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>UM 02172469</t>
+          <t>UM 03729356</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2013-2024</t>
+          <t>2015-2026</t>
         </is>
       </c>
     </row>
@@ -2669,43 +2685,43 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>63007085680074</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AE4688777</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>737100280</v>
+        <v>875613002</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>566528820</v>
+        <v>905181884</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Kitob tumani</t>
+          <t>Qashqadaryo, Kiuob tumani</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Oqsuv MFY, Yoshlar kuchasi, 156-uy</t>
+          <t>Ulubek MFY, Oʻrikzor koʻchasi, 23-uy</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Kitob tumani 32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>General Secondary School No. 46, Kitob District</t>
+          <t>General Secondary School No. 32, Kitob District</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -2715,76 +2731,10 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
+          <t>UM 03729007</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>2015-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Zarifova Marjona Samijon qizi</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>63007085680074</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>AE4688777</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>756130020</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>51818840</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Qashqadaryo, Kitob tumani</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Ulugʻbek MFY, Urigzor koʻchasi, 23 -uy</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Kitob tumani 32-sonli umumiy o'rta ta'lim maktabi</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>General Secondary School No. 32, Kitob District</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>Maktab</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>UM 03729007</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
